--- a/resultados/resultados_vcd.xlsx
+++ b/resultados/resultados_vcd.xlsx
@@ -525,7 +525,7 @@
     <t xml:space="preserve">Metodologia</t>
   </si>
   <si>
-    <t xml:space="preserve">N = 10 repetições por teste, intercaladas, com uma corrida de aquecimento descartada (perfil "medio": sysbench 10 s; fio 3 s + 15 s; iperf3 10 s).</t>
+    <t xml:space="preserve">N = 10 repetições por teste, intercaladas, com uma corrida de aquecimento descartada (sysbench 10 s; fio 3 s + 15 s; iperf3 10 s).</t>
   </si>
   <si>
     <t xml:space="preserve">Desvio-padrão amostral corrigido (STDEV); IC95 = t(0,975; N−1) × σ / √N; teste t de Welch bilateral (TTEST tipo 3); significativo se p &lt; 0,05.</t>
